--- a/data/trans_bre/P32B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,97</t>
+          <t>-2,14; 6,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -3,5</t>
+          <t>-14,04; -3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 2,3</t>
+          <t>-9,0; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,46</t>
+          <t>-8,07; -0,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,89</t>
+          <t>-100,0; -21,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 58,1</t>
+          <t>-84,2; 60,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,44</t>
+          <t>-4,06; -0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -1,26</t>
+          <t>-5,52; -1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,0</t>
+          <t>-6,88; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,88</t>
+          <t>-5,95; 1,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,18</t>
+          <t>-100,0; 102,02</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,27</t>
+          <t>-2,74; 2,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,0</t>
+          <t>-3,32; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,18</t>
+          <t>-2,06; 1,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-4,38; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -1,47</t>
+          <t>-8,69; -1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -1,05</t>
+          <t>-9,73; -1,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,96</t>
+          <t>-1,48; 5,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,0</t>
+          <t>-2,58; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,33</t>
+          <t>-3,6; 1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,73</t>
+          <t>-2,49; 4,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 591,2</t>
+          <t>-100,0; 499,45</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,46</t>
+          <t>-4,91; 0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,89</t>
+          <t>-3,57; 1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,77</t>
+          <t>-3,46; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-92,12; 73,81</t>
+          <t>-100,0; 29,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 121,41</t>
+          <t>-77,74; 120,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-93,2; 183,74</t>
+          <t>-92,33; 165,41</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,04</t>
+          <t>-0,24; 2,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,09</t>
+          <t>-3,12; 0,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,43</t>
+          <t>-2,89; -0,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,79</t>
+          <t>-1,22; 3,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,87</t>
+          <t>-100,0; 105,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,13</t>
+          <t>-0,46; 1,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -1,28</t>
+          <t>-3,14; -1,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; -0,17</t>
+          <t>-1,94; -0,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,53</t>
+          <t>-1,9; 0,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 229,68</t>
+          <t>-46,95; 198,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -51,14</t>
+          <t>-90,03; -46,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -6,63</t>
+          <t>-75,0; -5,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 38,15</t>
+          <t>-74,6; 26,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-94,08%</t>
+          <t>-79,3%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,79</t>
+          <t>-2,47; 6,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -3,12</t>
+          <t>-14,47; -4,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 2,34</t>
+          <t>-9,11; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -0,56</t>
+          <t>-6,19; 0,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,9</t>
+          <t>-100,0; -26,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-84,2; 60,97</t>
+          <t>-83,12; 71,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; -0,4</t>
+          <t>-4,06; -0,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; -1,25</t>
+          <t>-5,71; -1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-3,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-56,03%</t>
+          <t>-63,41%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,25</t>
+          <t>-7,49; 0,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,02</t>
+          <t>-100,0; 16,01</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,15%</t>
+          <t>-8,78%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,33</t>
+          <t>-2,73; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>-2,43; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,0</t>
+          <t>-3,23; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,18</t>
+          <t>-1,46; 1,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,0</t>
+          <t>-4,64; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -1,49</t>
+          <t>-8,67; -1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; -1,0</t>
+          <t>-9,95; -1,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,6</t>
+          <t>-1,78; 5,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-2,86; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,76</t>
+          <t>-3,73; 1,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,35</t>
+          <t>-2,85; 3,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 499,45</t>
+          <t>-100,0; 515,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-20,31%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,34</t>
+          <t>-4,81; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,81</t>
+          <t>-3,64; 2,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,49</t>
+          <t>-2,53; 5,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,65</t>
+          <t>-92,53; 53,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 120,86</t>
+          <t>-79,23; 131,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-92,33; 165,41</t>
+          <t>-62,02; 262,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,88</t>
+          <t>-0,16; 3,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,25</t>
+          <t>-3,15; 0,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,43</t>
+          <t>-2,95; -0,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,5</t>
+          <t>-1,2; 3,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,45</t>
+          <t>-100,0; 68,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-32,79%</t>
+          <t>-12,52%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,11</t>
+          <t>-0,49; 1,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -1,22</t>
+          <t>-3,12; -1,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,18</t>
+          <t>-1,99; -0,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,44</t>
+          <t>-1,39; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 198,62</t>
+          <t>-48,24; 199,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-90,03; -46,31</t>
+          <t>-89,95; -46,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-75,0; -5,95</t>
+          <t>-75,36; -1,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 26,98</t>
+          <t>-54,2; 69,77</t>
         </is>
       </c>
     </row>
